--- a/Filtered_V3.0/COCMHB_HCA_Florida_Mercy_Hospital.xlsx
+++ b/Filtered_V3.0/COCMHB_HCA_Florida_Mercy_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">* (*** DO NOT REMOVE ***)-Admissions </t>
+          <t>* (*** DO NOT REMOVE ***)-ADMO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,7 +1997,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2064,22 +2079,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AngelEye (NICU CameraSystem)-Admissions </t>
+          <t>AngelEye (NICU CameraSystem)-ADMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3159,7 +3159,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3181,7 +3196,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3226,22 +3241,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3698,22 +3698,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Admissions </t>
+          <t>GE (CPN - Gold Standard)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Clinical Monitoring Results </t>
+          <t>GE (CPN - Gold Standard)-ITSHMRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-ITS HM Results </t>
+          <t>GE (CPN - Gold Standard)-LABRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Lab Results (Discrete) </t>
+          <t>GE (CPN - Gold Standard)-PCSCMI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4603,6 +4603,21 @@
       <c r="P55" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4624,7 +4639,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4674,17 +4689,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4706,7 +4721,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4751,22 +4766,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4788,7 +4803,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4870,7 +4885,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4915,22 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5419,17 +5419,17 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6030,22 +6030,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6401,6 +6401,21 @@
       <c r="P79" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6422,7 +6437,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6472,17 +6487,17 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6519,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6554,17 +6569,17 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6601,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6636,7 +6651,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -6646,7 +6661,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6668,7 +6683,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6718,7 +6733,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -6728,7 +6743,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6750,7 +6765,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6800,17 +6815,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6832,7 +6847,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6914,7 +6929,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6996,7 +7011,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7046,17 +7061,17 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7093,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7128,17 +7143,17 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7175,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7210,17 +7225,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7257,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7288,21 +7303,6 @@
       <c r="P90" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7432,6 +7432,21 @@
       <c r="P92" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7453,7 +7468,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7499,6 +7514,21 @@
       <c r="P93" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7550,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7570,17 +7600,17 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7602,7 +7632,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7652,17 +7682,17 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7714,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7766,7 +7796,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7816,7 +7846,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -7826,7 +7856,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7848,7 +7878,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7898,7 +7928,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -7908,7 +7938,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7930,7 +7960,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8012,7 +8042,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8062,17 +8092,17 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -8094,7 +8124,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8144,17 +8174,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8206,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8258,7 +8288,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8308,17 +8338,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8370,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8422,7 +8452,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8472,17 +8502,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8534,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8554,17 +8584,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8616,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8636,17 +8666,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8698,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8718,17 +8748,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8780,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8800,17 +8830,17 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8862,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8878,21 +8908,6 @@
       <c r="P110" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8929,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8960,21 +8975,6 @@
       <c r="P111" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9520,7 +9520,22 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9542,7 +9557,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9609,7 +9624,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9654,22 +9669,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITSHMRO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9943,6 +9943,21 @@
       <c r="P125" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9964,7 +9979,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10014,17 +10029,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10061,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10096,17 +10111,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10128,7 +10143,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10178,17 +10193,17 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10225,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10260,7 +10275,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10270,7 +10285,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10292,7 +10307,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10342,7 +10357,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10352,7 +10367,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10374,7 +10389,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10424,17 +10439,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10456,7 +10471,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10506,17 +10521,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10553,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10620,7 +10635,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10702,7 +10717,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10752,17 +10767,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10784,7 +10799,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10834,17 +10849,17 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10881,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10916,17 +10931,17 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10963,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10998,17 +11013,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11045,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11080,17 +11095,17 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11127,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11162,17 +11177,17 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11209,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11240,21 +11255,6 @@
       <c r="P141" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (HCA 5.6)-ITS HM Results </t>
+          <t>HCA D&amp;IS (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark to UDS PROi)-</t>
+          <t>HCA D&amp;IS (Waterpark to UDS PROi)-irfpai</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12141,6 +12141,21 @@
       <c r="P154" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -12162,7 +12177,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12212,17 +12227,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12259,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12294,17 +12309,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -12326,7 +12341,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12376,17 +12391,17 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12423,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12490,7 +12505,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12540,7 +12555,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -12550,7 +12565,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -12572,7 +12587,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12622,17 +12637,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -12654,7 +12669,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12704,17 +12719,17 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12736,7 +12751,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12786,17 +12801,17 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12833,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12873,12 +12888,12 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12915,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12950,17 +12965,17 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12982,7 +12997,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13064,7 +13079,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13114,17 +13129,17 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13161,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13196,17 +13211,17 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13243,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13278,17 +13293,17 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13325,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13360,17 +13375,17 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13407,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13438,21 +13453,6 @@
       <c r="P170" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom (Navacare Patient Flow)-Admissions </t>
+          <t>Hill-Rom (Navacare Patient Flow)-ADMO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16525,6 +16525,21 @@
       <c r="P211" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16546,7 +16561,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16596,17 +16611,17 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16628,7 +16643,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16678,7 +16693,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -16688,7 +16703,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16710,7 +16725,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16760,7 +16775,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -16770,7 +16785,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -16792,7 +16807,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16842,7 +16857,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -16852,7 +16867,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -16874,7 +16889,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16956,7 +16971,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -17006,17 +17021,17 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17038,7 +17053,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17084,21 +17099,6 @@
       <c r="P218" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-Admissions </t>
+          <t>IsoPrime (NeoData)-ADMO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-ITS HM Results </t>
+          <t>IsoPrime (NeoData)-ITSHMRO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-Lab Results (Discrete) </t>
+          <t>IsoPrime (NeoData)-LABRES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-Admissions </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ADMO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-ITS DI Results </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ITSDIRO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18276,6 +18276,21 @@
       <c r="P234" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -18297,7 +18312,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18347,17 +18362,17 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -18379,7 +18394,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18429,7 +18444,7 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -18439,7 +18454,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18461,7 +18476,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18511,7 +18526,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -18521,7 +18536,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -18543,7 +18558,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18593,7 +18608,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -18603,7 +18618,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18640,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18707,7 +18722,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18757,17 +18772,17 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -18789,7 +18804,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18835,21 +18850,6 @@
       <c r="P241" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Admissions </t>
+          <t>Net Health (Wound Care)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Netsmart (UDS PROi to PA)-Case Mix Group</t>
+          <t>Netsmart (UDS PROi to PA)-nan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nuance (Primordial)-</t>
+          <t>Nuance (Primordial)-ADMO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21172,6 +21172,21 @@
       <c r="P272" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -21193,7 +21208,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (Primordial)-Admissions </t>
+          <t>Nuance (Primordial)-ITSDIRO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21243,17 +21258,17 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -21275,7 +21290,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (Primordial)-ITS DI Results </t>
+          <t>Nuance (Primordial)-radord</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21321,21 +21336,6 @@
       <c r="P274" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21630,7 +21630,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -21964,6 +21964,21 @@
       <c r="P283" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21985,7 +22000,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22031,21 +22046,6 @@
       <c r="P284" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmapoint (XChangePoint)-Admissions </t>
+          <t>Pharmapoint (XChangePoint)-ADMO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Admissions </t>
+          <t>Provation (Apex)-ADMO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-ITS HM Results </t>
+          <t>Provation (Apex)-CWSO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22529,22 +22529,22 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -22566,7 +22566,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Scheduling </t>
+          <t>Provation (Apex)-ITSHMRO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22611,22 +22611,22 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siemens (RapidComm)-Admissions </t>
+          <t>Siemens (RapidComm)-ADMO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sisco (FastPass)-Admissions </t>
+          <t>Sisco (FastPass)-ADMO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Telcor (Quick-Link)-</t>
+          <t>Telcor (Quick-Link)-ADMO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23043,7 +23043,22 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -23065,7 +23080,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telcor (Quick-Link)-Admissions </t>
+          <t>Telcor (Quick-Link)-labpoc</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23110,22 +23125,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -23599,7 +23599,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varian (Aria)-Admissions </t>
+          <t>Varian (Aria)-ADMO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varian (Aria)-Charges </t>
+          <t>Varian (Aria)-ITSHMRO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -23957,17 +23957,17 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -23989,7 +23989,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varian (Aria)-ITS HM Results </t>
+          <t>Varian (Aria)-Patient Accounting</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -24039,17 +24039,17 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24426,7 +24426,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24672,7 +24672,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -24991,6 +24991,21 @@
       <c r="P324" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -25012,7 +25027,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -25062,17 +25077,17 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25109,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -25176,7 +25191,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -25258,7 +25273,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -25340,7 +25355,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -25390,17 +25405,17 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -25422,7 +25437,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -25472,17 +25487,17 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -25504,7 +25519,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -25554,17 +25569,17 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25601,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -25636,17 +25651,17 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -25668,7 +25683,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25714,21 +25729,6 @@
       <c r="P333" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -25812,7 +25812,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -25894,7 +25894,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -26038,7 +26038,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
